--- a/exp_m3_out/assist_17/module3_full.xlsx
+++ b/exp_m3_out/assist_17/module3_full.xlsx
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7773670105046214</v>
+        <v>0.777367021023902</v>
       </c>
       <c r="D2" t="n">
         <v>0.7116985522233713</v>
@@ -486,7 +486,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7773670159339274</v>
+        <v>0.7773670166125908</v>
       </c>
       <c r="D3" t="n">
         <v>0.7116985522233713</v>
@@ -505,7 +505,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.777367030185856</v>
+        <v>0.7773670193272437</v>
       </c>
       <c r="D4" t="n">
         <v>0.7116985522233713</v>
@@ -524,7 +524,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7773670169519223</v>
+        <v>0.7773670179699174</v>
       </c>
       <c r="D5" t="n">
         <v>0.7116985522233713</v>
@@ -543,7 +543,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7773670152552642</v>
+        <v>0.7773670206845704</v>
       </c>
       <c r="D6" t="n">
         <v>0.7116985522233713</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.777367014576601</v>
+        <v>0.7773670098259582</v>
       </c>
       <c r="D7" t="n">
         <v>0.7116985522233713</v>
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7642363826895262</v>
+        <v>0.7642363687769294</v>
       </c>
       <c r="D8" t="n">
         <v>0.7001034126163392</v>
@@ -600,7 +600,7 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7644445690922634</v>
+        <v>0.7644445694315951</v>
       </c>
       <c r="D9" t="n">
         <v>0.7009694932781799</v>
@@ -619,7 +619,7 @@
         <v>0.3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7621985703551201</v>
+        <v>0.7621985693371252</v>
       </c>
       <c r="D10" t="n">
         <v>0.6997026887280248</v>
@@ -638,13 +638,13 @@
         <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7651495590589058</v>
+        <v>0.7651495502362835</v>
       </c>
       <c r="D11" t="n">
         <v>0.7026887280248191</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4428777052817973</v>
+        <v>0.4428777389280171</v>
       </c>
     </row>
   </sheetData>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7999254349281377</v>
+        <v>0.7999254305168265</v>
       </c>
       <c r="D2" t="n">
         <v>0.7291494312306102</v>
@@ -717,7 +717,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7688689296285921</v>
+        <v>0.7688689286105972</v>
       </c>
       <c r="D3" t="n">
         <v>0.7043821096173734</v>
@@ -736,7 +736,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7682911988640806</v>
+        <v>0.7682912070080398</v>
       </c>
       <c r="D4" t="n">
         <v>0.7036194415718717</v>
@@ -755,7 +755,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.768643030114732</v>
+        <v>0.7686430270607475</v>
       </c>
       <c r="D5" t="n">
         <v>0.7041235780765254</v>
@@ -774,7 +774,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7684989332770856</v>
+        <v>0.7684989271691164</v>
       </c>
       <c r="D6" t="n">
         <v>0.7050801447776629</v>
@@ -794,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +848,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>figs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -882,6 +887,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>If mask_effective=False, Exp-3B/3C are skipped as model-head defect.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>{'single_keep': ['qnoise_curve.png', 'qnoise_hard_curve.png', 'attribution_violin.png', 'attribution_ridge.png', 'interaction_heatmap.png', 'interaction_network.png', 'interaction_heatmap_global.png'], 'combo_added': ['fig_m3_qnoise_combo.png', 'fig_m3_interaction_global_combo.png']}</t>
         </is>
       </c>
     </row>

--- a/exp_m3_out/assist_17/module3_full.xlsx
+++ b/exp_m3_out/assist_17/module3_full.xlsx
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.777367021023902</v>
+        <v>0.7773670233992234</v>
       </c>
       <c r="D2" t="n">
         <v>0.7116985522233713</v>
@@ -486,7 +486,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7773670166125908</v>
+        <v>0.7773670213632335</v>
       </c>
       <c r="D3" t="n">
         <v>0.7116985522233713</v>
@@ -505,7 +505,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7773670193272437</v>
+        <v>0.7773670169519223</v>
       </c>
       <c r="D4" t="n">
         <v>0.7116985522233713</v>
@@ -524,7 +524,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7773670179699174</v>
+        <v>0.7773670244172183</v>
       </c>
       <c r="D5" t="n">
         <v>0.7116985522233713</v>
@@ -543,7 +543,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7773670206845704</v>
+        <v>0.7773670189879122</v>
       </c>
       <c r="D6" t="n">
         <v>0.7116985522233713</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7773670098259582</v>
+        <v>0.7773670210239019</v>
       </c>
       <c r="D7" t="n">
         <v>0.7116985522233713</v>
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7642363687769294</v>
+        <v>0.7642363840468528</v>
       </c>
       <c r="D8" t="n">
         <v>0.7001034126163392</v>
@@ -600,7 +600,7 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7644445694315951</v>
+        <v>0.7644445775755542</v>
       </c>
       <c r="D9" t="n">
         <v>0.7009694932781799</v>
@@ -619,7 +619,7 @@
         <v>0.3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7621985693371252</v>
+        <v>0.7621985594965079</v>
       </c>
       <c r="D10" t="n">
         <v>0.6997026887280248</v>
@@ -638,7 +638,7 @@
         <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7651495502362835</v>
+        <v>0.7651495546475946</v>
       </c>
       <c r="D11" t="n">
         <v>0.7026887280248191</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7999254305168265</v>
+        <v>0.7999254322134847</v>
       </c>
       <c r="D2" t="n">
         <v>0.7291494312306102</v>
@@ -717,7 +717,7 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7688689286105972</v>
+        <v>0.768868923181291</v>
       </c>
       <c r="D3" t="n">
         <v>0.7043821096173734</v>
@@ -736,7 +736,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7682912070080398</v>
+        <v>0.7682912005607387</v>
       </c>
       <c r="D4" t="n">
         <v>0.7036194415718717</v>
@@ -755,7 +755,7 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7686430270607475</v>
+        <v>0.768643031132727</v>
       </c>
       <c r="D5" t="n">
         <v>0.7041235780765254</v>
@@ -774,7 +774,7 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7684989271691164</v>
+        <v>0.7684989417603765</v>
       </c>
       <c r="D6" t="n">
         <v>0.7050801447776629</v>
